--- a/outputs/tables/tab-12-cursos-extremos.xlsx
+++ b/outputs/tables/tab-12-cursos-extremos.xlsx
@@ -408,10 +408,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>656</v>
+        <v>450</v>
       </c>
       <c r="E2">
-        <v>0.4542682926829268</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>1071</v>
+        <v>741</v>
       </c>
       <c r="E3">
-        <v>0.361344537815126</v>
+        <v>0.4048582995951417</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -465,23 +465,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia de Bauru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Farmácia - Bioquímica</t>
+          <t>Fonoaudiologia</t>
         </is>
       </c>
       <c r="D4">
-        <v>836</v>
+        <v>314</v>
       </c>
       <c r="E4">
-        <v>0.3480861244019139</v>
+        <v>0.4012738853503185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Farmácia - Bioquímica (Ribeirão Preto)</t>
+          <t>Fonoaudiologia (Bauru)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -493,28 +493,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
+          <t>Instituto de Arquitetura e Urbanismo de São Carlos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medicina Veterinária</t>
+          <t>Arquitetura e Urbanismo</t>
         </is>
       </c>
       <c r="D5">
-        <v>838</v>
+        <v>384</v>
       </c>
       <c r="E5">
-        <v>0.3317422434367542</v>
+        <v>0.4010416666666667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Medicina Veterinária (Pirassununga)</t>
+          <t>Arquitetura e Urbanismo (São Carlos)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>1098</v>
+        <v>767</v>
       </c>
       <c r="E6">
-        <v>0.3306010928961748</v>
+        <v>0.3989569752281616</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -559,28 +559,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Instituto de Arquitetura e Urbanismo de São Carlos</t>
+          <t>Escola de Enfermagem de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arquitetura e Urbanismo</t>
+          <t>Bacharelado e Licenciatura em Enfermagem</t>
         </is>
       </c>
       <c r="D7">
-        <v>575</v>
+        <v>447</v>
       </c>
       <c r="E7">
-        <v>0.3286956521739131</v>
+        <v>0.3870246085011186</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arquitetura e Urbanismo (São Carlos)</t>
+          <t>Bacharelado e Licenciatura em Enfermagem</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -592,28 +592,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciências da Saúde</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Bauru</t>
+          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fonoaudiologia</t>
+          <t>Ciências Biológicas</t>
         </is>
       </c>
       <c r="D8">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E8">
-        <v>0.3284518828451883</v>
+        <v>0.3773584905660378</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fonoaudiologia (Bauru)</t>
+          <t>Ciências Biológicas (Ribeirão Preto)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -625,28 +625,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Faculdade de Filosofia, Ciências e Letras de Ribeirão Preto</t>
+          <t>Faculdade de Zootecnia e Engenharia de Alimentos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Medicina Veterinária</t>
         </is>
       </c>
       <c r="D9">
-        <v>651</v>
+        <v>580</v>
       </c>
       <c r="E9">
-        <v>0.3271889400921659</v>
+        <v>0.3586206896551724</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ciências Biológicas (Ribeirão Preto)</t>
+          <t>Medicina Veterinária (Pirassununga)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -663,23 +663,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Faculdade de Ciências Farmacêuticas de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fonoaudiologia</t>
+          <t>Farmácia - Bioquímica</t>
         </is>
       </c>
       <c r="D10">
-        <v>344</v>
+        <v>754</v>
       </c>
       <c r="E10">
-        <v>0.313953488372093</v>
+        <v>0.3488063660477453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fonoaudiologia (São Paulo)</t>
+          <t>Farmácia - Bioquímica (Ribeirão Preto)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -696,23 +696,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bacharelado e Licenciatura em Enfermagem</t>
+          <t>Odontologia</t>
         </is>
       </c>
       <c r="D11">
-        <v>672</v>
+        <v>730</v>
       </c>
       <c r="E11">
-        <v>0.3095238095238095</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bacharelado e Licenciatura em Enfermagem</t>
+          <t>Odontologia (Ribeirão Preto)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -729,23 +729,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina de Ribeirão Preto</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ciências Médicas - Ciclo Básico</t>
+          <t>Fisioterapia</t>
         </is>
       </c>
       <c r="D12">
-        <v>503</v>
+        <v>243</v>
       </c>
       <c r="E12">
-        <v>0.2982107355864811</v>
+        <v>0.3415637860082305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ciências Médicas - Ciclo Básico</t>
+          <t>Fisioterapia (São Paulo)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Faculdade de Odontologia de Ribeirão Preto</t>
+          <t>Faculdade de Odontologia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -771,14 +771,14 @@
         </is>
       </c>
       <c r="D13">
-        <v>1051</v>
+        <v>1214</v>
       </c>
       <c r="E13">
-        <v>0.2892483349191247</v>
+        <v>0.329489291598023</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odontologia (Ribeirão Preto)</t>
+          <t>Odontologia (São Paulo)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -795,23 +795,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Escola de Enfermagem de Ribeirão Preto</t>
+          <t>Faculdade de Medicina</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enfermagem</t>
+          <t>Fonoaudiologia</t>
         </is>
       </c>
       <c r="D14">
-        <v>1092</v>
+        <v>235</v>
       </c>
       <c r="E14">
-        <v>0.2875457875457875</v>
+        <v>0.3276595744680851</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enfermagem (Ribeirão Preto)</t>
+          <t>Fonoaudiologia (São Paulo)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -828,23 +828,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Faculdade de Medicina</t>
+          <t>Escola de Enfermagem de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fisioterapia</t>
+          <t>Enfermagem</t>
         </is>
       </c>
       <c r="D15">
-        <v>350</v>
+        <v>737</v>
       </c>
       <c r="E15">
-        <v>0.2857142857142857</v>
+        <v>0.3242876526458616</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fisioterapia (São Paulo)</t>
+          <t>Enfermagem (Ribeirão Preto)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -856,28 +856,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ciências Biológicas</t>
+          <t>Ciências da Saúde</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Biomédicas</t>
+          <t>Faculdade de Medicina de Ribeirão Preto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Biomédicas</t>
+          <t>Fisioterapia</t>
         </is>
       </c>
       <c r="D16">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="E16">
-        <v>0.2777777777777778</v>
+        <v>0.3206521739130435</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Biomédicas</t>
+          <t>Fisioterapia (Ribeirão Preto)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -889,28 +889,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Música Bacharelado</t>
+          <t>Matemática Aplicada - Bacharelado</t>
         </is>
       </c>
       <c r="D17">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="E17">
-        <v>0.04090909090909091</v>
+        <v>0.044</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Música Bacharelado</t>
+          <t>Matemática Aplicada - Bacharelado</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -927,23 +927,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Matemática Aplicada - Bacharelado</t>
+          <t>Bacharelado em Estatística</t>
         </is>
       </c>
       <c r="D18">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="E18">
-        <v>0.0392156862745098</v>
+        <v>0.04337349397590361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Matemática Aplicada - Bacharelado</t>
+          <t>Bacharelado em Estatística</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -955,28 +955,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Agrárias</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Instituto de Física</t>
+          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Física Licenciatura</t>
+          <t>Bacharelado em Administração</t>
         </is>
       </c>
       <c r="D19">
-        <v>1706</v>
+        <v>247</v>
       </c>
       <c r="E19">
-        <v>0.03868698710433763</v>
+        <v>0.04048582995951417</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Física Licenciatura</t>
+          <t>Bacharelado em Administração (Piracicaba)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -988,28 +988,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Linguística, Letras e Artes</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Escola de Comunicações e Artes</t>
+          <t>Instituto de Ciências Matemáticas e de Computação</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Bacharelado em Sistemas de Informação</t>
         </is>
       </c>
       <c r="D20">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="E20">
-        <v>0.03747072599531616</v>
+        <v>0.04</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Bacharelado em Sistemas de Informação (São Paulo)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>2115</v>
+        <v>1479</v>
       </c>
       <c r="E21">
-        <v>0.03735224586288416</v>
+        <v>0.03989181879648411</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1054,28 +1054,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ciências Sociais Aplicadas</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Atuariais</t>
+          <t>Gestão de Políticas Públicas</t>
         </is>
       </c>
       <c r="D22">
-        <v>698</v>
+        <v>1232</v>
       </c>
       <c r="E22">
-        <v>0.0329512893982808</v>
+        <v>0.03733766233766234</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bacharelado em Ciências Atuariais</t>
+          <t>Gestão de Políticas Públicas</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1087,28 +1087,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Ciências Sociais Aplicadas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Instituto de Ciências Matemáticas e de Computação</t>
+          <t>Faculdade de Economia, Administração, Contabilidade e Atuária</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bacharelado em Sistemas de Informação</t>
+          <t>Bacharelado em Ciências Atuariais</t>
         </is>
       </c>
       <c r="D23">
-        <v>673</v>
+        <v>491</v>
       </c>
       <c r="E23">
-        <v>0.03268945022288262</v>
+        <v>0.03462321792260693</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bacharelado em Sistemas de Informação (São Paulo)</t>
+          <t>Bacharelado em Ciências Atuariais</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1120,28 +1120,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ciências Agrárias</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Escola Superior de Agricultura "Luiz de Queiroz"</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bacharelado em Administração</t>
+          <t>Bacharelado em Lazer e Turismo</t>
         </is>
       </c>
       <c r="D24">
-        <v>421</v>
+        <v>1129</v>
       </c>
       <c r="E24">
-        <v>0.03087885985748218</v>
+        <v>0.03365810451727192</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bacharelado em Administração (Piracicaba)</t>
+          <t>Bacharelado em Lazer e Turismo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1153,28 +1153,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Interunidades de Licenciatura IFSC/IQSC/ICMC</t>
+          <t>Instituto de Física</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Licenciatura em Ciências Exatas</t>
+          <t>Física Licenciatura</t>
         </is>
       </c>
       <c r="D25">
-        <v>588</v>
+        <v>1187</v>
       </c>
       <c r="E25">
-        <v>0.0272108843537415</v>
+        <v>0.03201347935973041</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Licenciatura em Ciências Exatas</t>
+          <t>Física Licenciatura</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1191,23 +1191,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Interunidades de Licenciatura IFSC/IQSC/ICMC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bacharelado em Lazer e Turismo</t>
+          <t>Licenciatura em Ciências Exatas</t>
         </is>
       </c>
       <c r="D26">
-        <v>1586</v>
+        <v>414</v>
       </c>
       <c r="E26">
-        <v>0.02522068095838588</v>
+        <v>0.02898550724637681</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bacharelado em Lazer e Turismo</t>
+          <t>Licenciatura em Ciências Exatas</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1219,28 +1219,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Multidisciplinar</t>
+          <t>Ciências Exatas e da Terra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Escola de Artes, Ciências e Humanidades</t>
+          <t>Instituto de Geociências</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Licenciatura em Geociências e Educação Ambiental</t>
         </is>
       </c>
       <c r="D27">
-        <v>1610</v>
+        <v>434</v>
       </c>
       <c r="E27">
-        <v>0.02360248447204969</v>
+        <v>0.02764976958525346</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Licenciatura em Geociências e Educação Ambiental</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1252,28 +1252,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciências Exatas e da Terra</t>
+          <t>Multidisciplinar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Instituto de Matemática e Estatística</t>
+          <t>Escola de Artes, Ciências e Humanidades</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bacharelado em Matemática Aplicada e Computacional</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D28">
-        <v>878</v>
+        <v>1130</v>
       </c>
       <c r="E28">
-        <v>0.0193621867881549</v>
+        <v>0.02654867256637168</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bacharelado em Matemática Aplicada e Computacional</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1290,23 +1290,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Instituto de Geociências</t>
+          <t>Instituto de Matemática e Estatística</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Licenciatura em Geociências e Educação Ambiental</t>
+          <t>Bacharelado em Matemática Aplicada e Computacional</t>
         </is>
       </c>
       <c r="D29">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E29">
-        <v>0.0192</v>
+        <v>0.02086677367576244</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Licenciatura em Geociências e Educação Ambiental</t>
+          <t>Bacharelado em Matemática Aplicada e Computacional</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>2138</v>
+        <v>1483</v>
       </c>
       <c r="E30">
-        <v>0.009354536950420954</v>
+        <v>0.009440323668240054</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
